--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-diagnose.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-diagnose.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$258</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$240</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9851" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9176" uniqueCount="841">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Unknown region code '276'</t>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/StructureDefinition/Diagnose|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/StructureDefinition/Diagnose|2027.0.0-ballot</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -617,7 +617,7 @@
     <t>ReferenzPrimaerdiagnose</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {condition-related|5.3.0}
+    <t xml:space="preserve">Extension {condition-related|5.4.0}
 </t>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <t>Feststellungsdatum</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {condition-assertedDate|5.3.0}
+    <t xml:space="preserve">Extension {condition-assertedDate|5.4.0}
 </t>
   </si>
   <si>
@@ -1061,7 +1061,7 @@
     <t>Extended valueSet to allow value'terminal'/'end-stage' as additional information for a given cancer diagnosis.</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-extended-condition-severity-snomedct|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-extended-condition-severity-snomedct|2027.0.0-ballot</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -1183,7 +1183,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-icd10gm|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-icd10gm|2027.0.0-ballot</t>
   </si>
   <si>
     <t>ICD10GMDiagnoseKodiert</t>
@@ -1450,7 +1450,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-alphaid|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-alphaid|2027.0.0-ballot</t>
   </si>
   <si>
     <t>ALPHAIDKodiert</t>
@@ -1513,7 +1513,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/diagnoses-sct|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/diagnoses-sct|2027.0.0-ballot</t>
   </si>
   <si>
     <t>SNOMEDDiagnoseKodiert</t>
@@ -1560,7 +1560,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-orphanet|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-orphanet|2027.0.0-ballot</t>
   </si>
   <si>
     <t>ORPHANETDiagnoseKodiert</t>
@@ -1672,7 +1672,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite|5.3.0}
+    <t xml:space="preserve">Extension {bodySite|5.4.0}
 </t>
   </si>
   <si>
@@ -1695,7 +1695,7 @@
     <t>snomed-ct</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-bodystructure-snomed|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-bodystructure-snomed|2027.0.0-ballot</t>
   </si>
   <si>
     <t>Condition.bodySite.coding:snomed-ct.id</t>
@@ -1908,7 +1908,7 @@
     <t>Beginn</t>
   </si>
   <si>
-    <t>Geschätztes oder tatsächliches Datum oder Zeitraum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
+    <t>Geschätztes oder tatsächliches Datum oder Alter, an dem die Erkrankung begonnen hat.</t>
   </si>
   <si>
     <t>Age is generally used when the patient reports an age at which the Condition began to occur.</t>
@@ -1930,440 +1930,117 @@
     <t>FiveWs.init</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod</t>
-  </si>
-  <si>
-    <t>onsetPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
+    <t>Condition.onset[x]:onsetDateTime</t>
+  </si>
+  <si>
+    <t>onsetDateTime</t>
+  </si>
+  <si>
+    <t>Beginn Datum</t>
+  </si>
+  <si>
+    <t>Das Datum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Zeitraum.von</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge</t>
+  </si>
+  <si>
+    <t>onsetAge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age
 </t>
   </si>
   <si>
-    <t>Beginn Zeitraum</t>
-  </si>
-  <si>
-    <t>Der Zeitraum, in dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.id</t>
+    <t>Erkrankungsbeginn als Alter</t>
+  </si>
+  <si>
+    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.id</t>
   </si>
   <si>
     <t>Condition.onset[x].id</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.extension</t>
+    <t>Condition.onset[x]:onsetAge.extension</t>
   </si>
   <si>
     <t>Condition.onset[x].extension</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start</t>
-  </si>
-  <si>
-    <t>Starting time with inclusive boundary</t>
-  </si>
-  <si>
-    <t>The start of the period. The boundary is inclusive.</t>
-  </si>
-  <si>
-    <t>If the low element is missing, the meaning is that the low boundary is not known.</t>
-  </si>
-  <si>
-    <t>Period.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per-1
-</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum.von</t>
-  </si>
-  <si>
-    <t>DR.1</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.id</t>
-  </si>
-  <si>
-    <t>xml:id (or equivalent in JSON)</t>
-  </si>
-  <si>
-    <t>unique id for the element within a resource (for internal references)</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von</t>
-  </si>
-  <si>
-    <t>lebensphase-von</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn</t>
+  </si>
+  <si>
+    <t>Lebensphase-Beginn</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://fhir.de/StructureDefinition/lebensphase|1.6.0}
 </t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.url</t>
+    <t>Lebensphase des Erkrankungsbeginns</t>
+  </si>
+  <si>
+    <t>Alternative Angabe, wenn genauere Eingrenzungen des Zeitraums nicht möglich sind, insbesondere im Kontext anamnestischer Diagnosen</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.url</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.url</t>
   </si>
   <si>
     <t>http://fhir.de/StructureDefinition/lebensphase</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x]</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x]</t>
   </si>
   <si>
     <t>KlinischRelevanterZeitraum.Lebensphase.von</t>
   </si>
   <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding</t>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.onset[x].extension.value[x].coding</t>
   </si>
   <si>
     <t>Lebensphase</t>
   </si>
   <si>
     <t>http://fhir.de/ValueSet/lebensphase-de|1.6.0</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.extension:lebensphase-von.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.start.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].start.value</t>
-  </si>
-  <si>
-    <t>Primitive value for dateTime</t>
-  </si>
-  <si>
-    <t>The actual value</t>
-  </si>
-  <si>
-    <t>dateTime.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end</t>
-  </si>
-  <si>
-    <t>End time with inclusive boundary, if not ongoing</t>
-  </si>
-  <si>
-    <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
-  </si>
-  <si>
-    <t>The high value includes any matching date/time. i.e. 2012-02-03T10:00:00 is in a period that has an end value of 2012-02-03.</t>
-  </si>
-  <si>
-    <t>If the end of the period is missing, it means that the period is ongoing</t>
-  </si>
-  <si>
-    <t>Period.end</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Zeitraum.bis</t>
-  </si>
-  <si>
-    <t>DR.2</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis</t>
-  </si>
-  <si>
-    <t>lebensphase-bis</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x]</t>
-  </si>
-  <si>
-    <t>KlinischRelevanterZeitraum.Lebensphase.bis</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.extension:lebensphase-bis.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.extension.value[x].text</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetPeriod.end.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].end.value</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetDateTime</t>
-  </si>
-  <si>
-    <t>onsetDateTime</t>
-  </si>
-  <si>
-    <t>Beginn Datum</t>
-  </si>
-  <si>
-    <t>Das Datum, an dem die Erkrankung begonnen hat, nach Meinung des Klinikers.</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge</t>
-  </si>
-  <si>
-    <t>onsetAge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age
-</t>
-  </si>
-  <si>
-    <t>Erkrankungsbeginn als Alter</t>
-  </si>
-  <si>
-    <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn</t>
-  </si>
-  <si>
-    <t>Lebensphase-Beginn</t>
-  </si>
-  <si>
-    <t>Lebensphase des Erkrankungsbeginns</t>
-  </si>
-  <si>
-    <t>Alternative Angabe, wenn genauere Eingrenzungen des Zeitraums nicht möglich sind, insbesondere im Kontext anamnestischer Diagnosen</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.url</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x]</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].id</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].extension</t>
-  </si>
-  <si>
-    <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding</t>
-  </si>
-  <si>
-    <t>Condition.onset[x].extension.value[x].coding</t>
   </si>
   <si>
     <t>Condition.onset[x]:onsetAge.extension:Lebensphase-Beginn.value[x].coding.id</t>
@@ -2539,14 +2216,10 @@
     <t>Condition.abatement[x]</t>
   </si>
   <si>
-    <t>dateTime
-AgePeriodRangestring</t>
-  </si>
-  <si>
-    <t>When in resolution/remission</t>
-  </si>
-  <si>
-    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+    <t>Ende</t>
+  </si>
+  <si>
+    <t>Geschätztes oder tatsächliches Datum oder Alter, an dem die Erkrankung beendet wurde.</t>
   </si>
   <si>
     <t>There is no explicit distinction between resolution and remission because in many cases the distinction is not clear. Age is generally used when the patient reports an age at which the Condition abated.  If there is no abatement element, it is unknown whether the condition has resolved or entered remission; applications and users should generally assume that the condition is still valid.  When abatementString exists, it implies the condition is abated.</t>
@@ -2557,6 +2230,177 @@
   </si>
   <si>
     <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementDateTime</t>
+  </si>
+  <si>
+    <t>abatementDateTime</t>
+  </si>
+  <si>
+    <t>Ende Datum</t>
+  </si>
+  <si>
+    <t>Das Datum, an dem die Erkrankung beendet wurde.</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Zeitraum.bis</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge</t>
+  </si>
+  <si>
+    <t>abatementAge</t>
+  </si>
+  <si>
+    <t>Erkrankungsende als Alter</t>
+  </si>
+  <si>
+    <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende</t>
+  </si>
+  <si>
+    <t>Lebensphase-Ende</t>
+  </si>
+  <si>
+    <t>Lebensphase des Erkrankungsendes</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.url</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.url</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x]</t>
+  </si>
+  <si>
+    <t>KlinischRelevanterZeitraum.Lebensphase.bis</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.extension:Lebensphase-Ende.value[x].text</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].extension.value[x].text</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.value</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].value</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.comparator</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].comparator</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.unit</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].unit</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].system</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x]:abatementAge.code</t>
+  </si>
+  <si>
+    <t>Condition.abatement[x].code</t>
   </si>
   <si>
     <t>Condition.recordedDate</t>
@@ -3105,11 +2949,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP258"/>
+  <dimension ref="A1:AP240"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="79.40625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.20703125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.3046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.52734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3133,7 +2977,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="116.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="113.96484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -23781,7 +23625,7 @@
         <v>79</v>
       </c>
       <c r="AE172" t="s" s="2">
-        <v>357</v>
+        <v>116</v>
       </c>
       <c r="AF172" t="s" s="2">
         <v>602</v>
@@ -23847,13 +23691,13 @@
         <v>91</v>
       </c>
       <c r="K173" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="L173" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="L173" t="s" s="2">
+      <c r="M173" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N173" t="s" s="2">
         <v>606</v>
@@ -23921,7 +23765,7 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>609</v>
@@ -23939,14 +23783,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C174" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="B174" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
         <v>79</v>
       </c>
@@ -23958,24 +23804,26 @@
         <v>90</v>
       </c>
       <c r="H174" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>104</v>
+        <v>619</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>105</v>
+        <v>620</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N174" s="2"/>
+        <v>621</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>79</v>
@@ -24024,7 +23872,7 @@
         <v>79</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>107</v>
+        <v>602</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -24036,22 +23884,22 @@
         <v>79</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>79</v>
+        <v>609</v>
       </c>
       <c r="AM174" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>79</v>
+        <v>610</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>79</v>
+        <v>611</v>
       </c>
       <c r="AP174" t="s" s="2">
         <v>79</v>
@@ -24059,21 +23907,21 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>79</v>
@@ -24085,17 +23933,15 @@
         <v>79</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>79</v>
@@ -24132,31 +23978,31 @@
         <v>79</v>
       </c>
       <c r="AB175" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD175" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE175" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ175" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AK175" t="s" s="2">
         <v>79</v>
@@ -24177,44 +24023,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H176" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J176" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>624</v>
+        <v>111</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>625</v>
+        <v>112</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>626</v>
+        <v>113</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -24252,34 +24098,34 @@
         <v>79</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AC176" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AD176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE176" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>627</v>
+        <v>117</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>628</v>
+        <v>79</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>629</v>
+        <v>79</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>79</v>
@@ -24288,7 +24134,7 @@
         <v>79</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>630</v>
+        <v>79</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>79</v>
@@ -24299,12 +24145,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="C177" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="C177" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="D177" t="s" s="2">
         <v>79</v>
       </c>
@@ -24325,15 +24173,17 @@
         <v>79</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>104</v>
+        <v>628</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N177" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N177" t="s" s="2">
+        <v>630</v>
+      </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>79</v>
@@ -24382,19 +24232,19 @@
         <v>79</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH177" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI177" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>79</v>
@@ -24417,10 +24267,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24431,7 +24281,7 @@
         <v>80</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>79</v>
@@ -24443,13 +24293,13 @@
         <v>79</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -24488,29 +24338,31 @@
         <v>79</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AC178" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD178" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>79</v>
@@ -24531,28 +24383,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>634</v>
+      </c>
+      <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>79</v>
@@ -24561,15 +24411,17 @@
         <v>79</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>639</v>
+        <v>110</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>380</v>
+        <v>111</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N179" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>79</v>
@@ -24606,16 +24458,16 @@
         <v>79</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AF179" t="s" s="2">
         <v>117</v>
@@ -24651,12 +24503,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="180" hidden="true">
+    <row r="180">
       <c r="A180" t="s" s="2">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24664,13 +24516,13 @@
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>79</v>
@@ -24679,22 +24531,24 @@
         <v>79</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>105</v>
+        <v>204</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N180" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>79</v>
+        <v>637</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>79</v>
@@ -24736,10 +24590,10 @@
         <v>79</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>90</v>
@@ -24769,26 +24623,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="181" hidden="true">
+    <row r="181">
       <c r="A181" t="s" s="2">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>79</v>
@@ -24797,17 +24651,15 @@
         <v>79</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
         <v>79</v>
@@ -24844,34 +24696,34 @@
         <v>79</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>117</v>
+        <v>214</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>197</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>79</v>
+        <v>640</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>79</v>
@@ -24889,12 +24741,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24902,13 +24754,13 @@
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G182" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H182" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I182" t="s" s="2">
         <v>79</v>
@@ -24917,24 +24769,22 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N182" s="2"/>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
-        <v>646</v>
+        <v>79</v>
       </c>
       <c r="S182" t="s" s="2">
         <v>79</v>
@@ -24976,10 +24826,10 @@
         <v>79</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>208</v>
+        <v>107</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>90</v>
@@ -25009,26 +24859,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G183" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>79</v>
@@ -25037,15 +24887,17 @@
         <v>79</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>240</v>
+        <v>110</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>212</v>
+        <v>111</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N183" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>79</v>
@@ -25082,34 +24934,34 @@
         <v>79</v>
       </c>
       <c r="AB183" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AD183" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE183" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>214</v>
+        <v>117</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>197</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>649</v>
+        <v>79</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>79</v>
@@ -25127,12 +24979,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="184" hidden="true">
+    <row r="184">
       <c r="A184" t="s" s="2">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25140,31 +24992,35 @@
       </c>
       <c r="E184" s="2"/>
       <c r="F184" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G184" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H184" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I184" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>105</v>
+        <v>256</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N184" s="2"/>
-      <c r="O184" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P184" t="s" s="2">
         <v>79</v>
       </c>
@@ -25188,13 +25044,13 @@
         <v>79</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>79</v>
+        <v>647</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>79</v>
+        <v>648</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>79</v>
@@ -25212,19 +25068,19 @@
         <v>79</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>107</v>
+        <v>260</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
         <v>79</v>
@@ -25236,7 +25092,7 @@
         <v>79</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>79</v>
+        <v>261</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>79</v>
@@ -25247,21 +25103,21 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G185" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H185" t="s" s="2">
         <v>79</v>
@@ -25273,17 +25129,15 @@
         <v>79</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
         <v>79</v>
@@ -25320,31 +25174,31 @@
         <v>79</v>
       </c>
       <c r="AB185" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC185" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD185" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE185" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH185" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI185" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ185" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AK185" t="s" s="2">
         <v>79</v>
@@ -25365,48 +25219,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O186" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
         <v>79</v>
       </c>
@@ -25430,31 +25282,31 @@
         <v>79</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>244</v>
+        <v>79</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>656</v>
+        <v>79</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>657</v>
+        <v>79</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB186" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AC186" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AD186" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE186" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>260</v>
+        <v>117</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -25466,7 +25318,7 @@
         <v>197</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>79</v>
@@ -25478,7 +25330,7 @@
         <v>79</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>79</v>
@@ -25487,12 +25339,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="187" hidden="true">
+    <row r="187">
       <c r="A187" t="s" s="2">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25500,31 +25352,35 @@
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G187" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I187" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>105</v>
+        <v>265</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N187" s="2"/>
-      <c r="O187" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P187" t="s" s="2">
         <v>79</v>
       </c>
@@ -25572,7 +25428,7 @@
         <v>79</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>107</v>
+        <v>269</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -25581,10 +25437,10 @@
         <v>90</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>79</v>
@@ -25596,7 +25452,7 @@
         <v>79</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>79</v>
+        <v>270</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>79</v>
@@ -25607,21 +25463,21 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G188" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H188" t="s" s="2">
         <v>79</v>
@@ -25630,19 +25486,19 @@
         <v>79</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>111</v>
+        <v>272</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>112</v>
+        <v>273</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>113</v>
+        <v>274</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -25680,31 +25536,31 @@
         <v>79</v>
       </c>
       <c r="AB188" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC188" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD188" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE188" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>117</v>
+        <v>275</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH188" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI188" t="s" s="2">
         <v>197</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>79</v>
@@ -25716,7 +25572,7 @@
         <v>79</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>79</v>
+        <v>276</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>79</v>
@@ -25727,10 +25583,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25753,19 +25609,19 @@
         <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>267</v>
+        <v>402</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>79</v>
@@ -25814,7 +25670,7 @@
         <v>79</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -25838,7 +25694,7 @@
         <v>79</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>79</v>
@@ -25849,10 +25705,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25878,15 +25734,17 @@
         <v>104</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O190" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P190" t="s" s="2">
         <v>79</v>
       </c>
@@ -25934,7 +25792,7 @@
         <v>79</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -25958,7 +25816,7 @@
         <v>79</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>79</v>
@@ -25967,12 +25825,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25980,13 +25838,13 @@
       </c>
       <c r="E191" s="2"/>
       <c r="F191" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G191" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>79</v>
@@ -25995,19 +25853,19 @@
         <v>91</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>165</v>
+        <v>290</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>402</v>
+        <v>293</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>79</v>
@@ -26056,7 +25914,7 @@
         <v>79</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -26080,7 +25938,7 @@
         <v>79</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>79</v>
@@ -26091,10 +25949,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26120,16 +25978,16 @@
         <v>104</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>402</v>
+        <v>300</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>79</v>
@@ -26178,7 +26036,7 @@
         <v>79</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -26202,7 +26060,7 @@
         <v>79</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>79</v>
@@ -26213,10 +26071,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26239,19 +26097,19 @@
         <v>91</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>290</v>
+        <v>667</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>291</v>
+        <v>668</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>292</v>
+        <v>669</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>293</v>
+        <v>670</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>294</v>
+        <v>671</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>79</v>
@@ -26300,7 +26158,7 @@
         <v>79</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>295</v>
+        <v>672</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -26309,7 +26167,7 @@
         <v>90</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ193" t="s" s="2">
         <v>102</v>
@@ -26324,7 +26182,7 @@
         <v>79</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>296</v>
+        <v>673</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>79</v>
@@ -26335,10 +26193,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26355,30 +26213,30 @@
         <v>79</v>
       </c>
       <c r="I194" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J194" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>298</v>
+        <v>676</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>677</v>
+      </c>
+      <c r="N194" s="2"/>
       <c r="O194" t="s" s="2">
-        <v>301</v>
+        <v>678</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q194" s="2"/>
+      <c r="Q194" t="s" s="2">
+        <v>679</v>
+      </c>
       <c r="R194" t="s" s="2">
         <v>79</v>
       </c>
@@ -26398,13 +26256,13 @@
         <v>79</v>
       </c>
       <c r="X194" t="s" s="2">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="Y194" t="s" s="2">
-        <v>79</v>
+        <v>680</v>
       </c>
       <c r="Z194" t="s" s="2">
-        <v>79</v>
+        <v>681</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>79</v>
@@ -26422,7 +26280,7 @@
         <v>79</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>302</v>
+        <v>682</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -26431,7 +26289,7 @@
         <v>90</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>102</v>
@@ -26446,7 +26304,7 @@
         <v>79</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>303</v>
+        <v>683</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>79</v>
@@ -26457,10 +26315,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>674</v>
+        <v>684</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26480,19 +26338,21 @@
         <v>79</v>
       </c>
       <c r="J195" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>676</v>
+        <v>686</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>677</v>
+        <v>687</v>
       </c>
       <c r="N195" s="2"/>
-      <c r="O195" s="2"/>
+      <c r="O195" t="s" s="2">
+        <v>688</v>
+      </c>
       <c r="P195" t="s" s="2">
         <v>79</v>
       </c>
@@ -26540,7 +26400,7 @@
         <v>79</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -26552,7 +26412,7 @@
         <v>79</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK195" t="s" s="2">
         <v>79</v>
@@ -26564,7 +26424,7 @@
         <v>79</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>79</v>
+        <v>690</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>79</v>
@@ -26573,12 +26433,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26592,7 +26452,7 @@
         <v>90</v>
       </c>
       <c r="H196" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I196" t="s" s="2">
         <v>79</v>
@@ -26601,24 +26461,22 @@
         <v>91</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="O196" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="N196" s="2"/>
+      <c r="O196" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="P196" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q196" t="s" s="2">
-        <v>684</v>
-      </c>
+      <c r="Q196" s="2"/>
       <c r="R196" t="s" s="2">
         <v>79</v>
       </c>
@@ -26662,7 +26520,7 @@
         <v>79</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -26671,13 +26529,13 @@
         <v>90</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>628</v>
+        <v>697</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>686</v>
+        <v>79</v>
       </c>
       <c r="AL196" t="s" s="2">
         <v>79</v>
@@ -26686,7 +26544,7 @@
         <v>79</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>79</v>
@@ -26697,10 +26555,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>688</v>
+        <v>698</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26720,19 +26578,23 @@
         <v>79</v>
       </c>
       <c r="J197" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>633</v>
+        <v>700</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="N197" s="2"/>
-      <c r="O197" s="2"/>
+        <v>701</v>
+      </c>
+      <c r="N197" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="O197" t="s" s="2">
+        <v>703</v>
+      </c>
       <c r="P197" t="s" s="2">
         <v>79</v>
       </c>
@@ -26780,7 +26642,7 @@
         <v>79</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>107</v>
+        <v>704</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
@@ -26792,7 +26654,7 @@
         <v>79</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK197" t="s" s="2">
         <v>79</v>
@@ -26804,7 +26666,7 @@
         <v>79</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>79</v>
+        <v>690</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>79</v>
@@ -26815,10 +26677,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>690</v>
+        <v>705</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>691</v>
+        <v>705</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26829,10 +26691,10 @@
         <v>80</v>
       </c>
       <c r="G198" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H198" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I198" t="s" s="2">
         <v>79</v>
@@ -26841,15 +26703,17 @@
         <v>79</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>110</v>
+        <v>603</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>188</v>
+        <v>706</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N198" s="2"/>
+        <v>707</v>
+      </c>
+      <c r="N198" t="s" s="2">
+        <v>708</v>
+      </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>79</v>
@@ -26886,7 +26750,7 @@
         <v>79</v>
       </c>
       <c r="AB198" t="s" s="2">
-        <v>114</v>
+        <v>607</v>
       </c>
       <c r="AC198" s="2"/>
       <c r="AD198" t="s" s="2">
@@ -26896,22 +26760,22 @@
         <v>116</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>117</v>
+        <v>705</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>79</v>
+        <v>709</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>79</v>
+        <v>608</v>
       </c>
       <c r="AL198" t="s" s="2">
         <v>79</v>
@@ -26923,7 +26787,7 @@
         <v>79</v>
       </c>
       <c r="AO198" t="s" s="2">
-        <v>79</v>
+        <v>710</v>
       </c>
       <c r="AP198" t="s" s="2">
         <v>79</v>
@@ -26931,13 +26795,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>692</v>
+        <v>711</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>691</v>
+        <v>705</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>693</v>
+        <v>712</v>
       </c>
       <c r="D199" t="s" s="2">
         <v>79</v>
@@ -26959,15 +26823,17 @@
         <v>79</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>639</v>
+        <v>225</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>380</v>
+        <v>713</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N199" s="2"/>
+        <v>714</v>
+      </c>
+      <c r="N199" t="s" s="2">
+        <v>708</v>
+      </c>
       <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
         <v>79</v>
@@ -27016,22 +26882,22 @@
         <v>79</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>117</v>
+        <v>705</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>197</v>
+        <v>709</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>79</v>
+        <v>715</v>
       </c>
       <c r="AL199" t="s" s="2">
         <v>79</v>
@@ -27043,20 +26909,22 @@
         <v>79</v>
       </c>
       <c r="AO199" t="s" s="2">
-        <v>79</v>
+        <v>710</v>
       </c>
       <c r="AP199" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="200" hidden="true">
+    <row r="200">
       <c r="A200" t="s" s="2">
-        <v>694</v>
+        <v>716</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="C200" s="2"/>
+        <v>705</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>717</v>
+      </c>
       <c r="D200" t="s" s="2">
         <v>79</v>
       </c>
@@ -27068,7 +26936,7 @@
         <v>90</v>
       </c>
       <c r="H200" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I200" t="s" s="2">
         <v>79</v>
@@ -27077,15 +26945,17 @@
         <v>79</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>104</v>
+        <v>619</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>105</v>
+        <v>718</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N200" s="2"/>
+        <v>719</v>
+      </c>
+      <c r="N200" t="s" s="2">
+        <v>708</v>
+      </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>79</v>
@@ -27134,7 +27004,7 @@
         <v>79</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>107</v>
+        <v>705</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -27143,10 +27013,10 @@
         <v>90</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>79</v>
+        <v>709</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK200" t="s" s="2">
         <v>79</v>
@@ -27161,7 +27031,7 @@
         <v>79</v>
       </c>
       <c r="AO200" t="s" s="2">
-        <v>79</v>
+        <v>710</v>
       </c>
       <c r="AP200" t="s" s="2">
         <v>79</v>
@@ -27169,21 +27039,21 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>696</v>
+        <v>720</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>697</v>
+        <v>721</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E201" s="2"/>
       <c r="F201" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H201" t="s" s="2">
         <v>79</v>
@@ -27195,17 +27065,15 @@
         <v>79</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N201" s="2"/>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
         <v>79</v>
@@ -27242,31 +27110,31 @@
         <v>79</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC201" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD201" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AK201" t="s" s="2">
         <v>79</v>
@@ -27287,26 +27155,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>698</v>
+        <v>722</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>699</v>
+        <v>723</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E202" s="2"/>
       <c r="F202" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H202" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I202" t="s" s="2">
         <v>79</v>
@@ -27315,16 +27183,16 @@
         <v>79</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
@@ -27332,7 +27200,7 @@
       </c>
       <c r="Q202" s="2"/>
       <c r="R202" t="s" s="2">
-        <v>646</v>
+        <v>79</v>
       </c>
       <c r="S202" t="s" s="2">
         <v>79</v>
@@ -27362,31 +27230,31 @@
         <v>79</v>
       </c>
       <c r="AB202" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AC202" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AD202" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE202" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ202" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AK202" t="s" s="2">
         <v>79</v>
@@ -27407,26 +27275,28 @@
         <v>79</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>700</v>
+        <v>724</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="C203" s="2"/>
+        <v>723</v>
+      </c>
+      <c r="C203" t="s" s="2">
+        <v>725</v>
+      </c>
       <c r="D203" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G203" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H203" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I203" t="s" s="2">
         <v>79</v>
@@ -27435,15 +27305,17 @@
         <v>79</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>240</v>
+        <v>628</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>212</v>
+        <v>726</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N203" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N203" t="s" s="2">
+        <v>630</v>
+      </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
         <v>79</v>
@@ -27492,22 +27364,22 @@
         <v>79</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>214</v>
+        <v>117</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH203" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI203" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AK203" t="s" s="2">
-        <v>702</v>
+        <v>79</v>
       </c>
       <c r="AL203" t="s" s="2">
         <v>79</v>
@@ -27527,10 +27399,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>703</v>
+        <v>727</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>704</v>
+        <v>728</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27645,10 +27517,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>705</v>
+        <v>729</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>706</v>
+        <v>730</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27659,7 +27531,7 @@
         <v>80</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>79</v>
@@ -27765,10 +27637,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>707</v>
+        <v>731</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>708</v>
+        <v>732</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27788,29 +27660,27 @@
         <v>79</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>256</v>
+        <v>204</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>257</v>
+        <v>205</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O206" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q206" s="2"/>
       <c r="R206" t="s" s="2">
-        <v>79</v>
+        <v>637</v>
       </c>
       <c r="S206" t="s" s="2">
         <v>79</v>
@@ -27828,13 +27698,13 @@
         <v>79</v>
       </c>
       <c r="X206" t="s" s="2">
-        <v>244</v>
+        <v>79</v>
       </c>
       <c r="Y206" t="s" s="2">
-        <v>656</v>
+        <v>79</v>
       </c>
       <c r="Z206" t="s" s="2">
-        <v>657</v>
+        <v>79</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>79</v>
@@ -27852,19 +27722,19 @@
         <v>79</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>260</v>
+        <v>208</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>79</v>
@@ -27876,7 +27746,7 @@
         <v>79</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>79</v>
@@ -27885,12 +27755,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="207" hidden="true">
+    <row r="207">
       <c r="A207" t="s" s="2">
-        <v>709</v>
+        <v>733</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>710</v>
+        <v>734</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27898,13 +27768,13 @@
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G207" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H207" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I207" t="s" s="2">
         <v>79</v>
@@ -27913,13 +27783,13 @@
         <v>79</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -27970,7 +27840,7 @@
         <v>79</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -27979,13 +27849,13 @@
         <v>90</v>
       </c>
       <c r="AI207" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>79</v>
+        <v>735</v>
       </c>
       <c r="AL207" t="s" s="2">
         <v>79</v>
@@ -28005,21 +27875,21 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>711</v>
+        <v>736</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>712</v>
+        <v>737</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E208" s="2"/>
       <c r="F208" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G208" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H208" t="s" s="2">
         <v>79</v>
@@ -28031,17 +27901,15 @@
         <v>79</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>79</v>
@@ -28078,31 +27946,31 @@
         <v>79</v>
       </c>
       <c r="AB208" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC208" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD208" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE208" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH208" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>79</v>
@@ -28123,48 +27991,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>713</v>
+        <v>738</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>714</v>
+        <v>739</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H209" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>265</v>
+        <v>111</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>266</v>
+        <v>112</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>79</v>
       </c>
@@ -28200,31 +28066,31 @@
         <v>79</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>269</v>
+        <v>117</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>197</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>79</v>
@@ -28236,7 +28102,7 @@
         <v>79</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>270</v>
+        <v>79</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>79</v>
@@ -28245,12 +28111,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="210" hidden="true">
+    <row r="210">
       <c r="A210" t="s" s="2">
-        <v>715</v>
+        <v>740</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>716</v>
+        <v>741</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28258,13 +28124,13 @@
       </c>
       <c r="E210" s="2"/>
       <c r="F210" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G210" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H210" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I210" t="s" s="2">
         <v>79</v>
@@ -28273,18 +28139,20 @@
         <v>91</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O210" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O210" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P210" t="s" s="2">
         <v>79</v>
       </c>
@@ -28308,13 +28176,13 @@
         <v>79</v>
       </c>
       <c r="X210" t="s" s="2">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>79</v>
+        <v>647</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>79</v>
+        <v>648</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>79</v>
@@ -28332,13 +28200,13 @@
         <v>79</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>197</v>
@@ -28356,7 +28224,7 @@
         <v>79</v>
       </c>
       <c r="AN210" t="s" s="2">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="AO210" t="s" s="2">
         <v>79</v>
@@ -28365,12 +28233,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>717</v>
+        <v>742</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>718</v>
+        <v>743</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -28378,35 +28246,31 @@
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G211" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H211" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I211" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J211" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>278</v>
+        <v>105</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O211" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N211" s="2"/>
+      <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>79</v>
       </c>
@@ -28454,7 +28318,7 @@
         <v>79</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>281</v>
+        <v>107</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -28463,10 +28327,10 @@
         <v>90</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK211" t="s" s="2">
         <v>79</v>
@@ -28478,7 +28342,7 @@
         <v>79</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>79</v>
@@ -28489,21 +28353,21 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>719</v>
+        <v>744</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>720</v>
+        <v>745</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>79</v>
@@ -28512,23 +28376,21 @@
         <v>79</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>284</v>
+        <v>111</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>285</v>
+        <v>112</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O212" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>79</v>
       </c>
@@ -28564,31 +28426,31 @@
         <v>79</v>
       </c>
       <c r="AB212" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AC212" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AD212" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>287</v>
+        <v>117</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>197</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>79</v>
@@ -28600,7 +28462,7 @@
         <v>79</v>
       </c>
       <c r="AN212" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="AO212" t="s" s="2">
         <v>79</v>
@@ -28609,12 +28471,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="213" hidden="true">
+    <row r="213">
       <c r="A213" t="s" s="2">
-        <v>721</v>
+        <v>746</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>722</v>
+        <v>747</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28622,13 +28484,13 @@
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G213" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H213" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I213" t="s" s="2">
         <v>79</v>
@@ -28637,19 +28499,19 @@
         <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>290</v>
+        <v>131</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>79</v>
@@ -28698,7 +28560,7 @@
         <v>79</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -28722,7 +28584,7 @@
         <v>79</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>79</v>
@@ -28733,10 +28595,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>723</v>
+        <v>748</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>724</v>
+        <v>749</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28762,17 +28624,15 @@
         <v>104</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O214" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
         <v>79</v>
       </c>
@@ -28820,7 +28680,7 @@
         <v>79</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -28844,7 +28704,7 @@
         <v>79</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>79</v>
@@ -28853,12 +28713,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="215" hidden="true">
+    <row r="215">
       <c r="A215" t="s" s="2">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>726</v>
+        <v>751</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28866,31 +28726,35 @@
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G215" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H215" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I215" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J215" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>225</v>
+        <v>165</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>676</v>
+        <v>278</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N215" s="2"/>
-      <c r="O215" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N215" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="O215" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P215" t="s" s="2">
         <v>79</v>
       </c>
@@ -28938,7 +28802,7 @@
         <v>79</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>678</v>
+        <v>281</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -28947,10 +28811,10 @@
         <v>90</v>
       </c>
       <c r="AI215" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>79</v>
@@ -28962,7 +28826,7 @@
         <v>79</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>79</v>
@@ -28971,16 +28835,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>727</v>
+        <v>752</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C216" t="s" s="2">
-        <v>728</v>
-      </c>
+        <v>753</v>
+      </c>
+      <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
         <v>79</v>
       </c>
@@ -28992,7 +28854,7 @@
         <v>90</v>
       </c>
       <c r="H216" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I216" t="s" s="2">
         <v>79</v>
@@ -29001,18 +28863,20 @@
         <v>91</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>729</v>
+        <v>284</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>730</v>
+        <v>285</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O216" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O216" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P216" t="s" s="2">
         <v>79</v>
       </c>
@@ -29060,7 +28924,7 @@
         <v>79</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>602</v>
+        <v>287</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -29069,7 +28933,7 @@
         <v>90</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AJ216" t="s" s="2">
         <v>102</v>
@@ -29078,31 +28942,29 @@
         <v>79</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>609</v>
+        <v>79</v>
       </c>
       <c r="AM216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>610</v>
+        <v>288</v>
       </c>
       <c r="AO216" t="s" s="2">
-        <v>611</v>
+        <v>79</v>
       </c>
       <c r="AP216" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>731</v>
+        <v>754</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C217" t="s" s="2">
-        <v>732</v>
-      </c>
+        <v>755</v>
+      </c>
+      <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
         <v>79</v>
       </c>
@@ -29114,7 +28976,7 @@
         <v>90</v>
       </c>
       <c r="H217" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I217" t="s" s="2">
         <v>79</v>
@@ -29123,18 +28985,20 @@
         <v>91</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>733</v>
+        <v>290</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>734</v>
+        <v>291</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>735</v>
+        <v>292</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O217" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="O217" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P217" t="s" s="2">
         <v>79</v>
       </c>
@@ -29182,7 +29046,7 @@
         <v>79</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>602</v>
+        <v>295</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
@@ -29191,7 +29055,7 @@
         <v>90</v>
       </c>
       <c r="AI217" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AJ217" t="s" s="2">
         <v>102</v>
@@ -29200,16 +29064,16 @@
         <v>79</v>
       </c>
       <c r="AL217" t="s" s="2">
-        <v>609</v>
+        <v>79</v>
       </c>
       <c r="AM217" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>610</v>
+        <v>296</v>
       </c>
       <c r="AO217" t="s" s="2">
-        <v>611</v>
+        <v>79</v>
       </c>
       <c r="AP217" t="s" s="2">
         <v>79</v>
@@ -29217,10 +29081,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>619</v>
+        <v>757</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29240,19 +29104,23 @@
         <v>79</v>
       </c>
       <c r="J218" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K218" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>105</v>
+        <v>298</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N218" s="2"/>
-      <c r="O218" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N218" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O218" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P218" t="s" s="2">
         <v>79</v>
       </c>
@@ -29300,7 +29168,7 @@
         <v>79</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>80</v>
@@ -29309,10 +29177,10 @@
         <v>90</v>
       </c>
       <c r="AI218" t="s" s="2">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="AJ218" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK218" t="s" s="2">
         <v>79</v>
@@ -29324,7 +29192,7 @@
         <v>79</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>79</v>
+        <v>303</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>79</v>
@@ -29335,21 +29203,21 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>621</v>
+        <v>759</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E219" s="2"/>
       <c r="F219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G219" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H219" t="s" s="2">
         <v>79</v>
@@ -29358,21 +29226,23 @@
         <v>79</v>
       </c>
       <c r="J219" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>110</v>
+        <v>667</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>111</v>
+        <v>668</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>112</v>
+        <v>669</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O219" s="2"/>
+        <v>670</v>
+      </c>
+      <c r="O219" t="s" s="2">
+        <v>671</v>
+      </c>
       <c r="P219" t="s" s="2">
         <v>79</v>
       </c>
@@ -29408,31 +29278,31 @@
         <v>79</v>
       </c>
       <c r="AB219" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC219" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD219" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE219" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>117</v>
+        <v>672</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ219" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK219" t="s" s="2">
         <v>79</v>
@@ -29444,7 +29314,7 @@
         <v>79</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>79</v>
+        <v>673</v>
       </c>
       <c r="AO219" t="s" s="2">
         <v>79</v>
@@ -29455,14 +29325,12 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>738</v>
+        <v>760</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C220" t="s" s="2">
-        <v>739</v>
-      </c>
+        <v>761</v>
+      </c>
+      <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
         <v>79</v>
       </c>
@@ -29477,28 +29345,30 @@
         <v>79</v>
       </c>
       <c r="I220" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J220" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>639</v>
+        <v>165</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>740</v>
+        <v>676</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N220" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="O220" s="2"/>
+        <v>677</v>
+      </c>
+      <c r="N220" s="2"/>
+      <c r="O220" t="s" s="2">
+        <v>678</v>
+      </c>
       <c r="P220" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q220" s="2"/>
+      <c r="Q220" t="s" s="2">
+        <v>679</v>
+      </c>
       <c r="R220" t="s" s="2">
         <v>79</v>
       </c>
@@ -29518,13 +29388,13 @@
         <v>79</v>
       </c>
       <c r="X220" t="s" s="2">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="Y220" t="s" s="2">
-        <v>79</v>
+        <v>680</v>
       </c>
       <c r="Z220" t="s" s="2">
-        <v>79</v>
+        <v>681</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>79</v>
@@ -29542,19 +29412,19 @@
         <v>79</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>117</v>
+        <v>682</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI220" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ220" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK220" t="s" s="2">
         <v>79</v>
@@ -29566,7 +29436,7 @@
         <v>79</v>
       </c>
       <c r="AN220" t="s" s="2">
-        <v>79</v>
+        <v>683</v>
       </c>
       <c r="AO220" t="s" s="2">
         <v>79</v>
@@ -29577,10 +29447,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29600,19 +29470,21 @@
         <v>79</v>
       </c>
       <c r="J221" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K221" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>105</v>
+        <v>686</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>106</v>
+        <v>687</v>
       </c>
       <c r="N221" s="2"/>
-      <c r="O221" s="2"/>
+      <c r="O221" t="s" s="2">
+        <v>688</v>
+      </c>
       <c r="P221" t="s" s="2">
         <v>79</v>
       </c>
@@ -29660,7 +29532,7 @@
         <v>79</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>107</v>
+        <v>689</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
@@ -29672,7 +29544,7 @@
         <v>79</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK221" t="s" s="2">
         <v>79</v>
@@ -29684,7 +29556,7 @@
         <v>79</v>
       </c>
       <c r="AN221" t="s" s="2">
-        <v>79</v>
+        <v>690</v>
       </c>
       <c r="AO221" t="s" s="2">
         <v>79</v>
@@ -29695,21 +29567,21 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E222" s="2"/>
       <c r="F222" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>79</v>
@@ -29718,21 +29590,21 @@
         <v>79</v>
       </c>
       <c r="J222" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>111</v>
+        <v>693</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N222" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O222" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="N222" s="2"/>
+      <c r="O222" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="P222" t="s" s="2">
         <v>79</v>
       </c>
@@ -29768,31 +29640,31 @@
         <v>79</v>
       </c>
       <c r="AB222" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC222" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD222" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE222" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>117</v>
+        <v>696</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>197</v>
+        <v>697</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK222" t="s" s="2">
         <v>79</v>
@@ -29804,7 +29676,7 @@
         <v>79</v>
       </c>
       <c r="AN222" t="s" s="2">
-        <v>79</v>
+        <v>690</v>
       </c>
       <c r="AO222" t="s" s="2">
         <v>79</v>
@@ -29813,12 +29685,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>746</v>
+        <v>766</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29826,39 +29698,41 @@
       </c>
       <c r="E223" s="2"/>
       <c r="F223" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G223" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I223" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J223" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I223" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J223" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K223" t="s" s="2">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>204</v>
+        <v>700</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>205</v>
+        <v>701</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O223" s="2"/>
+        <v>702</v>
+      </c>
+      <c r="O223" t="s" s="2">
+        <v>703</v>
+      </c>
       <c r="P223" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q223" s="2"/>
       <c r="R223" t="s" s="2">
-        <v>646</v>
+        <v>79</v>
       </c>
       <c r="S223" t="s" s="2">
         <v>79</v>
@@ -29900,10 +29774,10 @@
         <v>79</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>208</v>
+        <v>704</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>90</v>
@@ -29912,7 +29786,7 @@
         <v>79</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK223" t="s" s="2">
         <v>79</v>
@@ -29924,7 +29798,7 @@
         <v>79</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>79</v>
+        <v>690</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>79</v>
@@ -29935,10 +29809,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>749</v>
+        <v>768</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29958,16 +29832,16 @@
         <v>79</v>
       </c>
       <c r="J224" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>212</v>
+        <v>769</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>213</v>
+        <v>770</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -30018,7 +29892,7 @@
         <v>79</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>214</v>
+        <v>768</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -30027,13 +29901,13 @@
         <v>90</v>
       </c>
       <c r="AI224" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ224" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>79</v>
+        <v>771</v>
       </c>
       <c r="AL224" t="s" s="2">
         <v>79</v>
@@ -30042,21 +29916,21 @@
         <v>79</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>79</v>
+        <v>772</v>
       </c>
       <c r="AO224" t="s" s="2">
-        <v>79</v>
+        <v>773</v>
       </c>
       <c r="AP224" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="225" hidden="true">
+    <row r="225">
       <c r="A225" t="s" s="2">
-        <v>750</v>
+        <v>774</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>751</v>
+        <v>774</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30070,24 +29944,26 @@
         <v>90</v>
       </c>
       <c r="H225" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I225" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J225" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>104</v>
+        <v>775</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>105</v>
+        <v>776</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N225" s="2"/>
+        <v>777</v>
+      </c>
+      <c r="N225" t="s" s="2">
+        <v>778</v>
+      </c>
       <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
         <v>79</v>
@@ -30136,7 +30012,7 @@
         <v>79</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>107</v>
+        <v>774</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -30148,7 +30024,7 @@
         <v>79</v>
       </c>
       <c r="AJ225" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK225" t="s" s="2">
         <v>79</v>
@@ -30163,50 +30039,50 @@
         <v>79</v>
       </c>
       <c r="AO225" t="s" s="2">
-        <v>79</v>
+        <v>779</v>
       </c>
       <c r="AP225" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="226" hidden="true">
+    <row r="226">
       <c r="A226" t="s" s="2">
-        <v>752</v>
+        <v>780</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E226" s="2"/>
       <c r="F226" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G226" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H226" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I226" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J226" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>110</v>
+        <v>775</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>111</v>
+        <v>781</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>112</v>
+        <v>782</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>113</v>
+        <v>783</v>
       </c>
       <c r="O226" s="2"/>
       <c r="P226" t="s" s="2">
@@ -30244,31 +30120,31 @@
         <v>79</v>
       </c>
       <c r="AB226" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC226" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD226" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE226" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>117</v>
+        <v>780</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH226" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI226" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ226" t="s" s="2">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="AK226" t="s" s="2">
         <v>79</v>
@@ -30280,21 +30156,21 @@
         <v>79</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>79</v>
+        <v>784</v>
       </c>
       <c r="AO226" t="s" s="2">
-        <v>79</v>
+        <v>785</v>
       </c>
       <c r="AP226" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>754</v>
+        <v>786</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30302,35 +30178,31 @@
       </c>
       <c r="E227" s="2"/>
       <c r="F227" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G227" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H227" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I227" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J227" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>143</v>
+        <v>787</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>256</v>
+        <v>788</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O227" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>789</v>
+      </c>
+      <c r="N227" s="2"/>
+      <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
         <v>79</v>
       </c>
@@ -30354,13 +30226,13 @@
         <v>79</v>
       </c>
       <c r="X227" t="s" s="2">
-        <v>244</v>
+        <v>79</v>
       </c>
       <c r="Y227" t="s" s="2">
-        <v>656</v>
+        <v>79</v>
       </c>
       <c r="Z227" t="s" s="2">
-        <v>657</v>
+        <v>79</v>
       </c>
       <c r="AA227" t="s" s="2">
         <v>79</v>
@@ -30378,7 +30250,7 @@
         <v>79</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>260</v>
+        <v>786</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
@@ -30387,10 +30259,10 @@
         <v>81</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>102</v>
+        <v>790</v>
       </c>
       <c r="AK227" t="s" s="2">
         <v>79</v>
@@ -30402,7 +30274,7 @@
         <v>79</v>
       </c>
       <c r="AN227" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="AO227" t="s" s="2">
         <v>79</v>
@@ -30413,10 +30285,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>757</v>
+        <v>791</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30531,10 +30403,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>758</v>
+        <v>792</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>759</v>
+        <v>792</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30604,16 +30476,16 @@
         <v>79</v>
       </c>
       <c r="AB229" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AC229" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AD229" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE229" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AF229" t="s" s="2">
         <v>117</v>
@@ -30625,7 +30497,7 @@
         <v>81</v>
       </c>
       <c r="AI229" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ229" t="s" s="2">
         <v>118</v>
@@ -30649,47 +30521,47 @@
         <v>79</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>760</v>
+        <v>793</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>761</v>
+        <v>793</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
-        <v>79</v>
+        <v>794</v>
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G230" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H230" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I230" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I230" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="J230" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>265</v>
+        <v>795</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>266</v>
+        <v>796</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>267</v>
+        <v>113</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>268</v>
+        <v>229</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>79</v>
@@ -30738,19 +30610,19 @@
         <v>79</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>269</v>
+        <v>797</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI230" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ230" t="s" s="2">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AK230" t="s" s="2">
         <v>79</v>
@@ -30762,7 +30634,7 @@
         <v>79</v>
       </c>
       <c r="AN230" t="s" s="2">
-        <v>270</v>
+        <v>79</v>
       </c>
       <c r="AO230" t="s" s="2">
         <v>79</v>
@@ -30773,10 +30645,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>762</v>
+        <v>798</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>763</v>
+        <v>798</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30796,20 +30668,18 @@
         <v>79</v>
       </c>
       <c r="J231" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>272</v>
+        <v>799</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N231" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="N231" s="2"/>
       <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
         <v>79</v>
@@ -30834,13 +30704,13 @@
         <v>79</v>
       </c>
       <c r="X231" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="Y231" t="s" s="2">
-        <v>79</v>
+        <v>801</v>
       </c>
       <c r="Z231" t="s" s="2">
-        <v>79</v>
+        <v>802</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>79</v>
@@ -30858,7 +30728,7 @@
         <v>79</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>275</v>
+        <v>798</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>80</v>
@@ -30867,7 +30737,7 @@
         <v>90</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>197</v>
+        <v>803</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>102</v>
@@ -30879,10 +30749,10 @@
         <v>79</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>79</v>
+        <v>804</v>
       </c>
       <c r="AN231" t="s" s="2">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="AO231" t="s" s="2">
         <v>79</v>
@@ -30891,12 +30761,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>764</v>
+        <v>805</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>765</v>
+        <v>805</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30904,35 +30774,31 @@
       </c>
       <c r="E232" s="2"/>
       <c r="F232" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G232" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H232" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I232" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J232" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>165</v>
+        <v>806</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>278</v>
+        <v>807</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N232" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O232" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>808</v>
+      </c>
+      <c r="N232" s="2"/>
+      <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
         <v>79</v>
       </c>
@@ -30980,16 +30846,16 @@
         <v>79</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>281</v>
+        <v>805</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH232" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>197</v>
+        <v>803</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>102</v>
@@ -31004,7 +30870,7 @@
         <v>79</v>
       </c>
       <c r="AN232" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AO232" t="s" s="2">
         <v>79</v>
@@ -31015,10 +30881,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>766</v>
+        <v>809</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>767</v>
+        <v>809</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -31038,23 +30904,19 @@
         <v>79</v>
       </c>
       <c r="J233" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>284</v>
+        <v>810</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O233" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>811</v>
+      </c>
+      <c r="N233" s="2"/>
+      <c r="O233" s="2"/>
       <c r="P233" t="s" s="2">
         <v>79</v>
       </c>
@@ -31078,13 +30940,13 @@
         <v>79</v>
       </c>
       <c r="X233" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="Y233" t="s" s="2">
-        <v>79</v>
+        <v>812</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>79</v>
+        <v>813</v>
       </c>
       <c r="AA233" t="s" s="2">
         <v>79</v>
@@ -31102,7 +30964,7 @@
         <v>79</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>287</v>
+        <v>809</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>80</v>
@@ -31111,7 +30973,7 @@
         <v>90</v>
       </c>
       <c r="AI233" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ233" t="s" s="2">
         <v>102</v>
@@ -31126,7 +30988,7 @@
         <v>79</v>
       </c>
       <c r="AN233" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="AO233" t="s" s="2">
         <v>79</v>
@@ -31137,10 +30999,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>768</v>
+        <v>814</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>769</v>
+        <v>814</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -31151,7 +31013,7 @@
         <v>80</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H234" t="s" s="2">
         <v>79</v>
@@ -31160,23 +31022,21 @@
         <v>79</v>
       </c>
       <c r="J234" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>290</v>
+        <v>787</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>291</v>
+        <v>815</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>292</v>
+        <v>816</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O234" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>817</v>
+      </c>
+      <c r="O234" s="2"/>
       <c r="P234" t="s" s="2">
         <v>79</v>
       </c>
@@ -31224,19 +31084,19 @@
         <v>79</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>295</v>
+        <v>814</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH234" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ234" t="s" s="2">
-        <v>102</v>
+        <v>818</v>
       </c>
       <c r="AK234" t="s" s="2">
         <v>79</v>
@@ -31248,7 +31108,7 @@
         <v>79</v>
       </c>
       <c r="AN234" t="s" s="2">
-        <v>296</v>
+        <v>79</v>
       </c>
       <c r="AO234" t="s" s="2">
         <v>79</v>
@@ -31259,10 +31119,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>770</v>
+        <v>819</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>771</v>
+        <v>819</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -31282,23 +31142,19 @@
         <v>79</v>
       </c>
       <c r="J235" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K235" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>298</v>
+        <v>105</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N235" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O235" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N235" s="2"/>
+      <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
         <v>79</v>
       </c>
@@ -31346,7 +31202,7 @@
         <v>79</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>302</v>
+        <v>107</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>80</v>
@@ -31355,10 +31211,10 @@
         <v>90</v>
       </c>
       <c r="AI235" t="s" s="2">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK235" t="s" s="2">
         <v>79</v>
@@ -31370,7 +31226,7 @@
         <v>79</v>
       </c>
       <c r="AN235" t="s" s="2">
-        <v>303</v>
+        <v>79</v>
       </c>
       <c r="AO235" t="s" s="2">
         <v>79</v>
@@ -31381,21 +31237,21 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>772</v>
+        <v>820</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>773</v>
+        <v>820</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>79</v>
@@ -31404,23 +31260,21 @@
         <v>79</v>
       </c>
       <c r="J236" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>774</v>
+        <v>110</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>775</v>
+        <v>111</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>776</v>
+        <v>112</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>778</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
         <v>79</v>
       </c>
@@ -31468,19 +31322,19 @@
         <v>79</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>779</v>
+        <v>117</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI236" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ236" t="s" s="2">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AK236" t="s" s="2">
         <v>79</v>
@@ -31492,7 +31346,7 @@
         <v>79</v>
       </c>
       <c r="AN236" t="s" s="2">
-        <v>780</v>
+        <v>79</v>
       </c>
       <c r="AO236" t="s" s="2">
         <v>79</v>
@@ -31503,21 +31357,21 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>781</v>
+        <v>821</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>782</v>
+        <v>821</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
-        <v>79</v>
+        <v>794</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>79</v>
@@ -31529,24 +31383,24 @@
         <v>91</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="N237" s="2"/>
+        <v>796</v>
+      </c>
+      <c r="N237" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O237" t="s" s="2">
-        <v>785</v>
+        <v>229</v>
       </c>
       <c r="P237" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q237" t="s" s="2">
-        <v>786</v>
-      </c>
+      <c r="Q237" s="2"/>
       <c r="R237" t="s" s="2">
         <v>79</v>
       </c>
@@ -31566,13 +31420,13 @@
         <v>79</v>
       </c>
       <c r="X237" t="s" s="2">
-        <v>244</v>
+        <v>79</v>
       </c>
       <c r="Y237" t="s" s="2">
-        <v>787</v>
+        <v>79</v>
       </c>
       <c r="Z237" t="s" s="2">
-        <v>788</v>
+        <v>79</v>
       </c>
       <c r="AA237" t="s" s="2">
         <v>79</v>
@@ -31590,19 +31444,19 @@
         <v>79</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI237" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ237" t="s" s="2">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="AK237" t="s" s="2">
         <v>79</v>
@@ -31614,7 +31468,7 @@
         <v>79</v>
       </c>
       <c r="AN237" t="s" s="2">
-        <v>790</v>
+        <v>79</v>
       </c>
       <c r="AO237" t="s" s="2">
         <v>79</v>
@@ -31625,10 +31479,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>791</v>
+        <v>822</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>792</v>
+        <v>822</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -31639,7 +31493,7 @@
         <v>80</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>79</v>
@@ -31651,18 +31505,16 @@
         <v>91</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>104</v>
+        <v>240</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>793</v>
+        <v>823</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>794</v>
+        <v>824</v>
       </c>
       <c r="N238" s="2"/>
-      <c r="O238" t="s" s="2">
-        <v>795</v>
-      </c>
+      <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
         <v>79</v>
       </c>
@@ -31686,13 +31538,13 @@
         <v>79</v>
       </c>
       <c r="X238" t="s" s="2">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="Y238" t="s" s="2">
-        <v>79</v>
+        <v>825</v>
       </c>
       <c r="Z238" t="s" s="2">
-        <v>79</v>
+        <v>826</v>
       </c>
       <c r="AA238" t="s" s="2">
         <v>79</v>
@@ -31710,16 +31562,16 @@
         <v>79</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>796</v>
+        <v>822</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH238" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>79</v>
+        <v>827</v>
       </c>
       <c r="AJ238" t="s" s="2">
         <v>102</v>
@@ -31728,16 +31580,16 @@
         <v>79</v>
       </c>
       <c r="AL238" t="s" s="2">
-        <v>79</v>
+        <v>828</v>
       </c>
       <c r="AM238" t="s" s="2">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="AN238" t="s" s="2">
-        <v>797</v>
+        <v>79</v>
       </c>
       <c r="AO238" t="s" s="2">
-        <v>79</v>
+        <v>829</v>
       </c>
       <c r="AP238" t="s" s="2">
         <v>79</v>
@@ -31745,10 +31597,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>798</v>
+        <v>830</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>799</v>
+        <v>830</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31759,7 +31611,7 @@
         <v>80</v>
       </c>
       <c r="G239" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H239" t="s" s="2">
         <v>79</v>
@@ -31771,18 +31623,16 @@
         <v>91</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>131</v>
+        <v>831</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>800</v>
+        <v>832</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="N239" s="2"/>
-      <c r="O239" t="s" s="2">
-        <v>802</v>
-      </c>
+      <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
         <v>79</v>
       </c>
@@ -31830,16 +31680,16 @@
         <v>79</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH239" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>804</v>
+        <v>827</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>102</v>
@@ -31854,21 +31704,21 @@
         <v>79</v>
       </c>
       <c r="AN239" t="s" s="2">
-        <v>797</v>
+        <v>79</v>
       </c>
       <c r="AO239" t="s" s="2">
-        <v>79</v>
+        <v>829</v>
       </c>
       <c r="AP239" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="240" hidden="true">
+    <row r="240">
       <c r="A240" t="s" s="2">
-        <v>805</v>
+        <v>834</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>806</v>
+        <v>834</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31879,32 +31729,28 @@
         <v>80</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H240" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I240" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J240" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>165</v>
+        <v>835</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>807</v>
+        <v>836</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="O240" t="s" s="2">
-        <v>810</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="N240" s="2"/>
+      <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
         <v>79</v>
       </c>
@@ -31952,13 +31798,13 @@
         <v>79</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>811</v>
+        <v>834</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH240" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI240" t="s" s="2">
         <v>79</v>
@@ -31967,2170 +31813,26 @@
         <v>102</v>
       </c>
       <c r="AK240" t="s" s="2">
-        <v>79</v>
+        <v>838</v>
       </c>
       <c r="AL240" t="s" s="2">
-        <v>79</v>
+        <v>839</v>
       </c>
       <c r="AM240" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN240" t="s" s="2">
-        <v>797</v>
+        <v>840</v>
       </c>
       <c r="AO240" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP240" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="241" hidden="true">
-      <c r="A241" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="C241" s="2"/>
-      <c r="D241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E241" s="2"/>
-      <c r="F241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G241" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K241" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="L241" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="O241" s="2"/>
-      <c r="P241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q241" s="2"/>
-      <c r="R241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF241" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="AG241" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH241" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI241" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AJ241" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN241" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO241" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="AP241" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="C242" s="2"/>
-      <c r="D242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E242" s="2"/>
-      <c r="F242" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G242" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H242" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J242" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K242" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="L242" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="N242" s="2"/>
-      <c r="O242" s="2"/>
-      <c r="P242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q242" s="2"/>
-      <c r="R242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF242" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="AG242" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH242" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ242" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK242" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="AL242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM242" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN242" t="s" s="2">
-        <v>823</v>
-      </c>
-      <c r="AO242" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="AP242" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="C243" s="2"/>
-      <c r="D243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E243" s="2"/>
-      <c r="F243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G243" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H243" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J243" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K243" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="L243" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="N243" t="s" s="2">
-        <v>829</v>
-      </c>
-      <c r="O243" s="2"/>
-      <c r="P243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q243" s="2"/>
-      <c r="R243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF243" t="s" s="2">
-        <v>825</v>
-      </c>
-      <c r="AG243" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH243" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ243" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN243" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO243" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="AP243" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="C244" s="2"/>
-      <c r="D244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E244" s="2"/>
-      <c r="F244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G244" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H244" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J244" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K244" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="L244" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="M244" t="s" s="2">
-        <v>833</v>
-      </c>
-      <c r="N244" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="O244" s="2"/>
-      <c r="P244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q244" s="2"/>
-      <c r="R244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF244" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="AG244" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH244" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ244" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM244" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN244" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="AO244" t="s" s="2">
-        <v>836</v>
-      </c>
-      <c r="AP244" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="245" hidden="true">
-      <c r="A245" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="B245" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="C245" s="2"/>
-      <c r="D245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E245" s="2"/>
-      <c r="F245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G245" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K245" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="L245" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="M245" t="s" s="2">
-        <v>840</v>
-      </c>
-      <c r="N245" s="2"/>
-      <c r="O245" s="2"/>
-      <c r="P245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q245" s="2"/>
-      <c r="R245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF245" t="s" s="2">
-        <v>837</v>
-      </c>
-      <c r="AG245" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH245" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ245" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="AK245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO245" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP245" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="246" hidden="true">
-      <c r="A246" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="B246" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="C246" s="2"/>
-      <c r="D246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E246" s="2"/>
-      <c r="F246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G246" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K246" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L246" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M246" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N246" s="2"/>
-      <c r="O246" s="2"/>
-      <c r="P246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q246" s="2"/>
-      <c r="R246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF246" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG246" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH246" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO246" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP246" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="247" hidden="true">
-      <c r="A247" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="C247" s="2"/>
-      <c r="D247" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="E247" s="2"/>
-      <c r="F247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G247" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K247" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L247" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M247" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N247" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O247" s="2"/>
-      <c r="P247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q247" s="2"/>
-      <c r="R247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF247" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG247" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH247" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ247" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO247" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP247" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="248" hidden="true">
-      <c r="A248" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="B248" t="s" s="2">
-        <v>844</v>
-      </c>
-      <c r="C248" s="2"/>
-      <c r="D248" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="E248" s="2"/>
-      <c r="F248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G248" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I248" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J248" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K248" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L248" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="M248" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="N248" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O248" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="P248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q248" s="2"/>
-      <c r="R248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF248" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="AG248" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH248" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ248" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO248" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP248" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="249" hidden="true">
-      <c r="A249" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="C249" s="2"/>
-      <c r="D249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E249" s="2"/>
-      <c r="F249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G249" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K249" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="L249" t="s" s="2">
-        <v>850</v>
-      </c>
-      <c r="M249" t="s" s="2">
-        <v>851</v>
-      </c>
-      <c r="N249" s="2"/>
-      <c r="O249" s="2"/>
-      <c r="P249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q249" s="2"/>
-      <c r="R249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X249" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y249" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="Z249" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="AA249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF249" t="s" s="2">
-        <v>849</v>
-      </c>
-      <c r="AG249" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH249" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI249" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="AJ249" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM249" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="AN249" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AO249" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP249" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="250" hidden="true">
-      <c r="A250" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="B250" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="C250" s="2"/>
-      <c r="D250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E250" s="2"/>
-      <c r="F250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G250" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K250" t="s" s="2">
-        <v>857</v>
-      </c>
-      <c r="L250" t="s" s="2">
-        <v>858</v>
-      </c>
-      <c r="M250" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="N250" s="2"/>
-      <c r="O250" s="2"/>
-      <c r="P250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q250" s="2"/>
-      <c r="R250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF250" t="s" s="2">
-        <v>856</v>
-      </c>
-      <c r="AG250" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH250" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI250" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="AJ250" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP250" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="251" hidden="true">
-      <c r="A251" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="B251" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="C251" s="2"/>
-      <c r="D251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E251" s="2"/>
-      <c r="F251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G251" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K251" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="L251" t="s" s="2">
-        <v>861</v>
-      </c>
-      <c r="M251" t="s" s="2">
-        <v>862</v>
-      </c>
-      <c r="N251" s="2"/>
-      <c r="O251" s="2"/>
-      <c r="P251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q251" s="2"/>
-      <c r="R251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X251" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y251" t="s" s="2">
-        <v>863</v>
-      </c>
-      <c r="Z251" t="s" s="2">
-        <v>864</v>
-      </c>
-      <c r="AA251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF251" t="s" s="2">
-        <v>860</v>
-      </c>
-      <c r="AG251" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH251" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ251" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO251" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP251" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="252" hidden="true">
-      <c r="A252" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="C252" s="2"/>
-      <c r="D252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E252" s="2"/>
-      <c r="F252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G252" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K252" t="s" s="2">
-        <v>838</v>
-      </c>
-      <c r="L252" t="s" s="2">
-        <v>866</v>
-      </c>
-      <c r="M252" t="s" s="2">
-        <v>867</v>
-      </c>
-      <c r="N252" t="s" s="2">
-        <v>868</v>
-      </c>
-      <c r="O252" s="2"/>
-      <c r="P252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q252" s="2"/>
-      <c r="R252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF252" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="AG252" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH252" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ252" t="s" s="2">
-        <v>869</v>
-      </c>
-      <c r="AK252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO252" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP252" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="253" hidden="true">
-      <c r="A253" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>870</v>
-      </c>
-      <c r="C253" s="2"/>
-      <c r="D253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E253" s="2"/>
-      <c r="F253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G253" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K253" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L253" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M253" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N253" s="2"/>
-      <c r="O253" s="2"/>
-      <c r="P253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q253" s="2"/>
-      <c r="R253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF253" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG253" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH253" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO253" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP253" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="254" hidden="true">
-      <c r="A254" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>871</v>
-      </c>
-      <c r="C254" s="2"/>
-      <c r="D254" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="E254" s="2"/>
-      <c r="F254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G254" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K254" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L254" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M254" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N254" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O254" s="2"/>
-      <c r="P254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q254" s="2"/>
-      <c r="R254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF254" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AG254" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH254" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ254" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO254" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP254" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="255" hidden="true">
-      <c r="A255" t="s" s="2">
-        <v>872</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>872</v>
-      </c>
-      <c r="C255" s="2"/>
-      <c r="D255" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="E255" s="2"/>
-      <c r="F255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G255" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I255" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J255" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K255" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L255" t="s" s="2">
-        <v>846</v>
-      </c>
-      <c r="M255" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="N255" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O255" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="P255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q255" s="2"/>
-      <c r="R255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF255" t="s" s="2">
-        <v>848</v>
-      </c>
-      <c r="AG255" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH255" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ255" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO255" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP255" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="256" hidden="true">
-      <c r="A256" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="B256" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="C256" s="2"/>
-      <c r="D256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E256" s="2"/>
-      <c r="F256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G256" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J256" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K256" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="L256" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="M256" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="N256" s="2"/>
-      <c r="O256" s="2"/>
-      <c r="P256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q256" s="2"/>
-      <c r="R256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X256" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y256" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="Z256" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="AA256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF256" t="s" s="2">
-        <v>873</v>
-      </c>
-      <c r="AG256" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH256" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI256" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="AJ256" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL256" t="s" s="2">
-        <v>879</v>
-      </c>
-      <c r="AM256" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AN256" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO256" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="AP256" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="257" hidden="true">
-      <c r="A257" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="B257" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="C257" s="2"/>
-      <c r="D257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E257" s="2"/>
-      <c r="F257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G257" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J257" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K257" t="s" s="2">
-        <v>882</v>
-      </c>
-      <c r="L257" t="s" s="2">
-        <v>883</v>
-      </c>
-      <c r="M257" t="s" s="2">
-        <v>884</v>
-      </c>
-      <c r="N257" s="2"/>
-      <c r="O257" s="2"/>
-      <c r="P257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q257" s="2"/>
-      <c r="R257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF257" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="AG257" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH257" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI257" t="s" s="2">
-        <v>878</v>
-      </c>
-      <c r="AJ257" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN257" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO257" t="s" s="2">
-        <v>880</v>
-      </c>
-      <c r="AP257" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="B258" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="C258" s="2"/>
-      <c r="D258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E258" s="2"/>
-      <c r="F258" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G258" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H258" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K258" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="L258" t="s" s="2">
-        <v>887</v>
-      </c>
-      <c r="M258" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="N258" s="2"/>
-      <c r="O258" s="2"/>
-      <c r="P258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q258" s="2"/>
-      <c r="R258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF258" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="AG258" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH258" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ258" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK258" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="AL258" t="s" s="2">
-        <v>890</v>
-      </c>
-      <c r="AM258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN258" t="s" s="2">
-        <v>891</v>
-      </c>
-      <c r="AO258" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP258" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP258">
+  <autoFilter ref="A1:AP240">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -34140,7 +31842,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI257">
+  <conditionalFormatting sqref="A2:AI239">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
